--- a/src/test/resources/testData/TaskCreationTestData.xlsx
+++ b/src/test/resources/testData/TaskCreationTestData.xlsx
@@ -8,24 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishal\Desktop\SeleniumAutomation\eclipse-workspace\AdvanceFrameWorkDesign\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA1873B-EF28-4C7A-B867-943507EC79A3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E203D44F-3186-43D8-9DBC-3A7F123BAC5B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{5F7D3B99-D034-441B-B1F7-06ED4F3CD305}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{5F7D3B99-D034-441B-B1F7-06ED4F3CD305}"/>
   </bookViews>
   <sheets>
     <sheet name="TaskCreationData" sheetId="1" r:id="rId1"/>
+    <sheet name="RegistrationForm" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="68">
   <si>
     <t>Sr No</t>
   </si>
@@ -130,13 +140,112 @@
   </si>
   <si>
     <t>administrator</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Marital</t>
+  </si>
+  <si>
+    <t>Hobby</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>DobMonth</t>
+  </si>
+  <si>
+    <t>DobDay</t>
+  </si>
+  <si>
+    <t>DobYear</t>
+  </si>
+  <si>
+    <t>PhoneNumber</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>About</t>
+  </si>
+  <si>
+    <t>RePassword</t>
+  </si>
+  <si>
+    <t>Vishal</t>
+  </si>
+  <si>
+    <t>Vaibhav</t>
+  </si>
+  <si>
+    <t>Sayali</t>
+  </si>
+  <si>
+    <t>Shaha</t>
+  </si>
+  <si>
+    <t>Mehta</t>
+  </si>
+  <si>
+    <t>Married</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>Dance,Reading,Cricket</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>vshaha7171</t>
+  </si>
+  <si>
+    <t>test@gmail.com</t>
+  </si>
+  <si>
+    <t>Abc</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>vshaha7172</t>
+  </si>
+  <si>
+    <t>vshaha7173</t>
+  </si>
+  <si>
+    <t>xyz</t>
+  </si>
+  <si>
+    <t>qwe</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>dull</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Dance,Reading</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +274,12 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -676,4 +791,211 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15C5019C-B399-4FCB-898F-9431BAB86F42}">
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2014</v>
+      </c>
+      <c r="J2">
+        <v>6572537422</v>
+      </c>
+      <c r="K2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2014</v>
+      </c>
+      <c r="J3">
+        <v>6572537429</v>
+      </c>
+      <c r="K3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N3" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2014</v>
+      </c>
+      <c r="J4">
+        <v>6572537428</v>
+      </c>
+      <c r="K4" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M4" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="L2" r:id="rId1" xr:uid="{7A6B7AAC-43DA-4B32-A1B2-8FEA3F9240A4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/testData/TaskCreationTestData.xlsx
+++ b/src/test/resources/testData/TaskCreationTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishal\Desktop\SeleniumAutomation\eclipse-workspace\AdvanceFrameWorkDesign\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E203D44F-3186-43D8-9DBC-3A7F123BAC5B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB197A4-3E8D-447C-9D4B-0B0CF59116CD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{5F7D3B99-D034-441B-B1F7-06ED4F3CD305}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="67">
   <si>
     <t>Sr No</t>
   </si>
@@ -184,15 +184,9 @@
     <t>Vaibhav</t>
   </si>
   <si>
-    <t>Sayali</t>
-  </si>
-  <si>
     <t>Shaha</t>
   </si>
   <si>
-    <t>Mehta</t>
-  </si>
-  <si>
     <t>Married</t>
   </si>
   <si>
@@ -239,6 +233,9 @@
   </si>
   <si>
     <t>Dance,Reading</t>
+  </si>
+  <si>
+    <t>Aaryan</t>
   </si>
 </sst>
 </file>
@@ -858,16 +855,16 @@
         <v>47</v>
       </c>
       <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
         <v>50</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
-        <v>54</v>
-      </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -882,19 +879,19 @@
         <v>6572537422</v>
       </c>
       <c r="K2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2" t="s">
         <v>56</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="N2" t="s">
         <v>57</v>
       </c>
-      <c r="M2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N2" t="s">
-        <v>59</v>
-      </c>
       <c r="O2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -905,16 +902,16 @@
         <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" t="s">
         <v>53</v>
-      </c>
-      <c r="E3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -929,19 +926,19 @@
         <v>6572537429</v>
       </c>
       <c r="K3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" t="s">
         <v>60</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N3" t="s">
-        <v>62</v>
-      </c>
       <c r="O3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -949,19 +946,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
         <v>49</v>
       </c>
-      <c r="C4" t="s">
-        <v>51</v>
-      </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -976,19 +973,19 @@
         <v>6572537428</v>
       </c>
       <c r="K4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" t="s">
         <v>61</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M4" t="s">
-        <v>65</v>
-      </c>
-      <c r="N4" t="s">
-        <v>63</v>
-      </c>
       <c r="O4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
